--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,9 +793,1004 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136953672</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43318</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>558568</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6988385</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953672</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136953671</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>558564</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6988385</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953671</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136953677</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558703</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6988421</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953677</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136953700</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558698</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6988434</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953700</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136953674</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99355</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>558647</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6988407</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953674</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136953670</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558559</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6988381</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953670</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136953675</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558669</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6988412</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953675</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136953676</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558681</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6988416</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953676</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136953701</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövudden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558686</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6988430</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953701</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136953672</v>
       </c>
       <c r="B3" t="n">
-        <v>43318</v>
+        <v>43331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136953672</v>
       </c>
       <c r="B3" t="n">
-        <v>43331</v>
+        <v>43333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136953672</v>
       </c>
       <c r="B3" t="n">
-        <v>43333</v>
+        <v>43343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136953672</v>
       </c>
       <c r="B3" t="n">
-        <v>43343</v>
+        <v>43344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62079-2022 artfynd.xlsx
+++ b/artfynd/A 62079-2022 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136953671</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136953677</v>
       </c>
       <c r="B5" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>136953700</v>
       </c>
       <c r="B6" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136953674</v>
       </c>
       <c r="B7" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136953670</v>
       </c>
       <c r="B8" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>136953675</v>
       </c>
       <c r="B9" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136953676</v>
       </c>
       <c r="B10" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>136953701</v>
       </c>
       <c r="B11" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
